--- a/backend/templates/5.4_Template.xlsx
+++ b/backend/templates/5.4_Template.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Departmental Library (5.4)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="5.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,37 +26,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="0"/>
-      <sz val="16"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -65,28 +40,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
+        <fgColor rgb="00002060"/>
+        <bgColor rgb="00002060"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -95,83 +60,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -254,44 +171,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -318,15 +235,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -353,7 +269,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -365,142 +280,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -511,38 +450,39 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="57.109375" customWidth="1" min="1" max="1"/>
-    <col width="58.5546875" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" customHeight="1" thickBot="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 5.4 Departmental Library and No. of Books Procured in Library</t>
+          <t>5.4 DEPARTMENTAL LIBRARY AND NO. OF BOOKS PROCURED IN LIBRARY</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
     </row>
-    <row r="2" ht="27.75" customHeight="1" thickBot="1">
+    <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Documents to be Uploaded</t>
+          <t>Documents to be Uploaded</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evidence Link</t>
+          <t>Evidence Link</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="78.75" customHeight="1" thickBot="1">
+    <row r="3" ht="80" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.List of books available in the departmental library
- 2.Issue register
-</t>
+          <t>1. List of books available in the departmental library
+2. Issue register
+3. Approval document for books procurement during assessment year
+4. Verified list of books procured from library</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -552,58 +492,9 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="57.88671875" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38.25" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   5.6 No. of Books procured in the library</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="n"/>
-    </row>
-    <row r="2" ht="29.25" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Documents to be Uploaded</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Evidence Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="81" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1.Approval document for books procurement during
- assessment year
- 2.Verified list of books procured from library</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>to be uploaded on portal</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/backend/templates/5.4_Template.xlsx
+++ b/backend/templates/5.4_Template.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="5.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Departmental Library (5.4)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,12 +26,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color theme="0"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -40,18 +65,28 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00002060"/>
-        <bgColor rgb="00002060"/>
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -60,35 +95,83 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -171,44 +254,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -235,14 +318,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -269,6 +353,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -280,166 +365,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -450,51 +511,99 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="57.109375" customWidth="1" min="1" max="1"/>
+    <col width="58.5546875" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40.5" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 5.4 Departmental Library and No. of Books Procured in Library</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Documents to be Uploaded</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Evidence Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="78.75" customHeight="1" thickBot="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1.List of books available in the departmental library
+ 2.Issue register
+</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>to be uploaded on portal</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="57.88671875" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>5.4 DEPARTMENTAL LIBRARY AND NO. OF BOOKS PROCURED IN LIBRARY</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
+    <row r="1" ht="38.25" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   5.6 No. of Books procured in the library</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
     </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Documents to be Uploaded</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Evidence Link</t>
+    <row r="2" ht="29.25" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Documents to be Uploaded</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Evidence Link</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>1. List of books available in the departmental library
-2. Issue register
-3. Approval document for books procurement during assessment year
-4. Verified list of books procured from library</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+    <row r="3" ht="81" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1.Approval document for books procurement during
+ assessment year
+ 2.Verified list of books procured from library</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>to be uploaded on portal</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>